--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.50435542241517</v>
+        <v>2.519457756142465</v>
       </c>
       <c r="D2" t="n">
-        <v>12.57222713010941</v>
+        <v>2.042986908642779</v>
       </c>
       <c r="E2" t="n">
-        <v>4.236765678211404</v>
+        <v>0.6884744227093532</v>
       </c>
       <c r="F2" t="n">
-        <v>13.01448298560202</v>
+        <v>2.114853485160328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.08011955103514</v>
+        <v>4.07551942704321</v>
       </c>
       <c r="D3" t="n">
-        <v>40.98860236544874</v>
+        <v>6.660647884385421</v>
       </c>
       <c r="E3" t="n">
-        <v>4.236765678211404</v>
+        <v>0.6884744227093532</v>
       </c>
       <c r="F3" t="n">
-        <v>13.01448298560202</v>
+        <v>2.114853485160328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.75697144030541</v>
+        <v>3.86050785904963</v>
       </c>
       <c r="D4" t="n">
-        <v>39.29351456695477</v>
+        <v>6.385196117130151</v>
       </c>
       <c r="E4" t="n">
-        <v>4.236765678211404</v>
+        <v>0.6884744227093532</v>
       </c>
       <c r="F4" t="n">
-        <v>13.01448298560202</v>
+        <v>2.114853485160328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
